--- a/models/xls/BeModelClinicalReport.xlsx
+++ b/models/xls/BeModelClinicalReport.xlsx
@@ -503,7 +503,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
@@ -939,23 +938,11 @@
           <t>Data Element</t>
         </is>
       </c>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
-      <c r="I1" s="1" t="n"/>
-      <c r="J1" s="1" t="n"/>
-      <c r="K1" s="1" t="n"/>
-      <c r="L1" s="1" t="n"/>
-      <c r="M1" s="1" t="n"/>
       <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Common Glossary</t>
         </is>
       </c>
-      <c r="O1" s="1" t="n"/>
       <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Example Value</t>
@@ -1086,6 +1073,16 @@
           <t>*</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>BusinessIdentifier</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>equivalent</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1131,6 +1128,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>OriginatingRequest</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>equivalent</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1176,6 +1183,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>RecordedDate</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>equivalent</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1266,6 +1283,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Patient</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>equivalent</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1311,6 +1338,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Recorder</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>equivalent</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1491,6 +1528,16 @@
           <t>extensible</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>equivalent</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1546,6 +1593,16 @@
           <t>extensible</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>equivalent</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1636,6 +1693,16 @@
           <t>*</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>equivalent</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1734,6 +1801,16 @@
       <c r="M17" t="inlineStr">
         <is>
           <t>required</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>equivalent</t>
         </is>
       </c>
     </row>
